--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The unique ID of the Health Data Access Body permit (required if secondary use).</t>
+    <t>Records the identifier of an EHDS data permit associated with the documented secondary use, where applicable.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-data-permit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
